--- a/videographer_forms/003_video_recording_purchase_order--videographer_forms.xlsx
+++ b/videographer_forms/003_video_recording_purchase_order--videographer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>720p</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>720p</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>video_resolution_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wedding</t>
+          <t>corporate_event</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>Corporate Event</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>corporate_event</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Corporate Event</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>event_size_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>event_size_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>new_order</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>New Order</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>new_order</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Order</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1624,27 +1624,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>credit_card</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
